--- a/DSM2/ZOI/20260616/ChannelLength_Data.xlsx
+++ b/DSM2/ZOI/20260616/ChannelLength_Data.xlsx
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v/>
+        <v>652.2251893939394</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v/>
+        <v>0.9681975649349737</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v/>
+        <v>19.84090909090909</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v/>
+        <v>0.02945289476747226</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v/>
+        <v>1.582765151515152</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v/>
+        <v>0.002349540297554083</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -651,22 +651,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v/>
+        <v>651.2310606060606</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v/>
+        <v>0.9656521585281534</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v/>
+        <v>21.58125</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v/>
+        <v>0.03200090091962325</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v/>
+        <v>1.582765151515152</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v/>
+        <v>0.002346940552223289</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -758,22 +758,22 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v/>
+        <v>650.3598484848485</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v/>
+        <v>0.9643603161756075</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v/>
+        <v>22.45246212121212</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v/>
+        <v>0.03329274327216928</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v/>
+        <v>1.582765151515152</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v/>
+        <v>0.002346940552223289</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
